--- a/ROST.xlsx
+++ b/ROST.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EAFA02-B3AB-4677-BB19-46155A20020D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{776DE622-82C9-4B45-8B31-FA35E0F48108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{32D7F01B-6AE9-4EA4-A41D-85AC8D1A6BED}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{32D7F01B-6AE9-4EA4-A41D-85AC8D1A6BED}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -231,7 +231,7 @@
     <t>Q427</t>
   </si>
   <si>
-    <t>FQ127</t>
+    <t>FQ227</t>
   </si>
 </sst>
 </file>
@@ -243,13 +243,19 @@
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -443,49 +449,52 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -852,7 +861,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="2">
-        <v>232.02</v>
+        <v>249.68</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -863,9 +872,9 @@
         <v>2</v>
       </c>
       <c r="H4" s="3">
-        <v>319.95699999999999</v>
-      </c>
-      <c r="I4" s="29" t="s">
+        <v>317.68700000000001</v>
+      </c>
+      <c r="I4" s="30" t="s">
         <v>64</v>
       </c>
     </row>
@@ -878,7 +887,7 @@
       </c>
       <c r="H5" s="3">
         <f>H4*H3</f>
-        <v>74236.423139999999</v>
+        <v>79320.090160000007</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -886,9 +895,9 @@
         <v>4</v>
       </c>
       <c r="H6" s="3">
-        <v>4130.9799999999996</v>
-      </c>
-      <c r="I6" s="29" t="s">
+        <v>4288.1239999999998</v>
+      </c>
+      <c r="I6" s="30" t="s">
         <v>64</v>
       </c>
     </row>
@@ -903,10 +912,10 @@
         <v>5</v>
       </c>
       <c r="H7" s="3">
-        <f>776.843+241.344</f>
-        <v>1018.1869999999999</v>
-      </c>
-      <c r="I7" s="29" t="s">
+        <f>777.053+241.459</f>
+        <v>1018.5119999999999</v>
+      </c>
+      <c r="I7" s="30" t="s">
         <v>64</v>
       </c>
     </row>
@@ -926,7 +935,7 @@
       </c>
       <c r="H8" s="3">
         <f>H5-H6+H7</f>
-        <v>71123.630140000008</v>
+        <v>76050.478160000013</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -946,6 +955,12 @@
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B11" s="14"/>
       <c r="E11" s="15"/>
+      <c r="G11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B12" s="16"/>
@@ -956,12 +971,6 @@
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
@@ -1214,7 +1223,9 @@
       <c r="O5" s="21">
         <v>2282</v>
       </c>
-      <c r="P5" s="21"/>
+      <c r="P5" s="21">
+        <v>2328</v>
+      </c>
       <c r="Q5" s="21"/>
       <c r="R5" s="21"/>
       <c r="S5" s="21"/>
@@ -1308,7 +1319,9 @@
       <c r="O8" s="23">
         <v>6010.4759999999997</v>
       </c>
-      <c r="P8" s="23"/>
+      <c r="P8" s="23">
+        <v>6264.8860000000004</v>
+      </c>
       <c r="Q8" s="23"/>
       <c r="R8" s="23"/>
       <c r="S8" s="23"/>
@@ -1382,7 +1395,9 @@
       <c r="O9" s="28">
         <v>4230.5889999999999</v>
       </c>
-      <c r="P9" s="28"/>
+      <c r="P9" s="28">
+        <v>4145.2150000000001</v>
+      </c>
       <c r="Q9" s="28"/>
       <c r="R9" s="28"/>
       <c r="S9" s="3"/>
@@ -1446,7 +1461,7 @@
         <v>1437.0710000000004</v>
       </c>
       <c r="J10" s="3">
-        <f t="shared" ref="J10:O10" si="9">J8-J9</f>
+        <f t="shared" ref="J10:P10" si="9">J8-J9</f>
         <v>1568.6570000000029</v>
       </c>
       <c r="K10" s="3">
@@ -1469,7 +1484,10 @@
         <f t="shared" si="9"/>
         <v>1779.8869999999997</v>
       </c>
-      <c r="P10" s="3"/>
+      <c r="P10" s="3">
+        <f t="shared" si="9"/>
+        <v>2119.6710000000003</v>
+      </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="S10" s="23"/>
@@ -1553,7 +1571,9 @@
       <c r="O11" s="28">
         <v>975.86099999999999</v>
       </c>
-      <c r="P11" s="28"/>
+      <c r="P11" s="28">
+        <v>1016.053</v>
+      </c>
       <c r="Q11" s="28"/>
       <c r="R11" s="28"/>
       <c r="S11" s="3"/>
@@ -1617,7 +1637,7 @@
         <v>604.21600000000035</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" ref="J12:O12" si="18">J10-J11</f>
+        <f t="shared" ref="J12:P12" si="18">J10-J11</f>
         <v>731.02400000000307</v>
       </c>
       <c r="K12" s="3">
@@ -1640,7 +1660,10 @@
         <f t="shared" si="18"/>
         <v>804.02599999999973</v>
       </c>
-      <c r="P12" s="3"/>
+      <c r="P12" s="3">
+        <f t="shared" si="18"/>
+        <v>1103.6180000000004</v>
+      </c>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
       <c r="S12" s="23"/>
@@ -1724,7 +1747,9 @@
       <c r="O13" s="28">
         <v>33.448999999999998</v>
       </c>
-      <c r="P13" s="28"/>
+      <c r="P13" s="28">
+        <v>31.143999999999998</v>
+      </c>
       <c r="Q13" s="28"/>
       <c r="R13" s="28"/>
       <c r="S13" s="3"/>
@@ -1788,7 +1813,7 @@
         <v>646.74300000000039</v>
       </c>
       <c r="J14" s="3">
-        <f t="shared" ref="J14:O14" si="27">J12+J13</f>
+        <f t="shared" ref="J14:P14" si="27">J12+J13</f>
         <v>770.75600000000304</v>
       </c>
       <c r="K14" s="3">
@@ -1811,7 +1836,10 @@
         <f t="shared" si="27"/>
         <v>837.47499999999968</v>
       </c>
-      <c r="P14" s="3"/>
+      <c r="P14" s="3">
+        <f t="shared" si="27"/>
+        <v>1134.7620000000004</v>
+      </c>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
@@ -1895,7 +1923,9 @@
       <c r="O15" s="28">
         <v>187.511</v>
       </c>
-      <c r="P15" s="28"/>
+      <c r="P15" s="28">
+        <v>283.46300000000002</v>
+      </c>
       <c r="Q15" s="28"/>
       <c r="R15" s="28"/>
       <c r="S15" s="3"/>
@@ -1959,7 +1989,7 @@
         <v>488.80800000000039</v>
       </c>
       <c r="J16" s="3">
-        <f t="shared" ref="J16:O16" si="36">J14-J15</f>
+        <f t="shared" ref="J16:P16" si="36">J14-J15</f>
         <v>586.77500000000305</v>
       </c>
       <c r="K16" s="3">
@@ -1982,7 +2012,10 @@
         <f t="shared" si="36"/>
         <v>649.96399999999971</v>
       </c>
-      <c r="P16" s="3"/>
+      <c r="P16" s="3">
+        <f t="shared" si="36"/>
+        <v>851.29900000000043</v>
+      </c>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="23"/>
@@ -2051,7 +2084,7 @@
         <v>32</v>
       </c>
       <c r="C18" s="24">
-        <f t="shared" ref="C18:O18" si="38">C16/C19</f>
+        <f t="shared" ref="C18:P18" si="38">C16/C19</f>
         <v>1.100997192714664</v>
       </c>
       <c r="D18" s="24">
@@ -2102,7 +2135,10 @@
         <f t="shared" si="38"/>
         <v>2.0314104707820104</v>
       </c>
-      <c r="P18" s="24"/>
+      <c r="P18" s="24">
+        <f t="shared" si="38"/>
+        <v>2.6796784256201871</v>
+      </c>
       <c r="Q18" s="24"/>
       <c r="R18" s="24"/>
       <c r="S18" s="24"/>
@@ -2183,7 +2219,9 @@
       <c r="O19" s="3">
         <v>319.95699999999999</v>
       </c>
-      <c r="P19" s="3"/>
+      <c r="P19" s="3">
+        <v>317.68700000000001</v>
+      </c>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
@@ -2266,7 +2304,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L21" s="25">
-        <f t="shared" ref="L21:O21" si="42">+L5/H5-1</f>
+        <f t="shared" ref="L21:P21" si="42">+L5/H5-1</f>
         <v>3.9571694599627616E-2</v>
       </c>
       <c r="M21" s="25">
@@ -2281,7 +2319,10 @@
         <f t="shared" si="42"/>
         <v>3.4920634920635019E-2</v>
       </c>
-      <c r="P21" s="25"/>
+      <c r="P21" s="25">
+        <f t="shared" si="42"/>
+        <v>4.2543663233318485E-2</v>
+      </c>
       <c r="Q21" s="25"/>
       <c r="R21" s="25"/>
       <c r="S21" s="3"/>
@@ -2316,7 +2357,7 @@
         <v>8.084680442638259E-2</v>
       </c>
       <c r="H22" s="26">
-        <f t="shared" ref="H22:O22" si="43">H8/D8-1</f>
+        <f t="shared" ref="H22:P22" si="43">H8/D8-1</f>
         <v>7.1453047221780475E-2</v>
       </c>
       <c r="I22" s="26">
@@ -2347,7 +2388,10 @@
         <f t="shared" si="43"/>
         <v>0.205719351225915</v>
       </c>
-      <c r="P22" s="26"/>
+      <c r="P22" s="26">
+        <f t="shared" si="43"/>
+        <v>0.13306452779739097</v>
+      </c>
       <c r="Q22" s="26"/>
       <c r="R22" s="26"/>
       <c r="S22" s="3"/>
@@ -2434,10 +2478,13 @@
         <v>0.27190350674931307</v>
       </c>
       <c r="O23" s="25">
-        <f t="shared" ref="O23" si="48">O10/O8</f>
+        <f t="shared" ref="O23:P23" si="48">O10/O8</f>
         <v>0.2961307889757816</v>
       </c>
-      <c r="P23" s="25"/>
+      <c r="P23" s="25">
+        <f t="shared" si="48"/>
+        <v>0.33834151172104332</v>
+      </c>
       <c r="Q23" s="25"/>
       <c r="R23" s="25"/>
       <c r="S23" s="3"/>
@@ -2527,10 +2574,13 @@
         <v>0.12269101452944689</v>
       </c>
       <c r="O24" s="25">
-        <f t="shared" ref="O24" si="53">O12/O8</f>
+        <f t="shared" ref="O24:P24" si="53">O12/O8</f>
         <v>0.13377076956966466</v>
       </c>
-      <c r="P24" s="25"/>
+      <c r="P24" s="25">
+        <f t="shared" si="53"/>
+        <v>0.17615931079990926</v>
+      </c>
       <c r="Q24" s="25"/>
       <c r="R24" s="25"/>
       <c r="S24" s="3"/>
@@ -2620,10 +2670,13 @@
         <v>9.7334936832095223E-2</v>
       </c>
       <c r="O25" s="25">
-        <f t="shared" ref="O25" si="58">O16/O8</f>
+        <f t="shared" ref="O25:P25" si="58">O16/O8</f>
         <v>0.1081385234713523</v>
       </c>
-      <c r="P25" s="25"/>
+      <c r="P25" s="25">
+        <f t="shared" si="58"/>
+        <v>0.13588419645624841</v>
+      </c>
       <c r="Q25" s="25"/>
       <c r="R25" s="25"/>
       <c r="S25" s="3"/>
@@ -2713,10 +2766,13 @@
         <v>0.23860019333694876</v>
       </c>
       <c r="O26" s="25">
-        <f t="shared" ref="O26" si="63">O15/O14</f>
+        <f t="shared" ref="O26:P26" si="63">O15/O14</f>
         <v>0.22390041493775942</v>
       </c>
-      <c r="P26" s="25"/>
+      <c r="P26" s="25">
+        <f t="shared" si="63"/>
+        <v>0.24979951743184908</v>
+      </c>
       <c r="Q26" s="25"/>
       <c r="R26" s="25"/>
       <c r="S26" s="3"/>
